--- a/artfynd/A 9217-2025 artfynd.xlsx
+++ b/artfynd/A 9217-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1972006</v>
+        <v>199922</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585854.1859792606</v>
+        <v>585944</v>
       </c>
       <c r="R2" t="n">
-        <v>7226133.844853232</v>
+        <v>7226155</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2011-07-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-07-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,7 +760,7 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1972003</v>
+        <v>364888</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585996.4936643523</v>
+        <v>585943</v>
       </c>
       <c r="R3" t="n">
-        <v>7225979.678255401</v>
+        <v>7226051</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2011-07-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2011-07-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,7 +861,7 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -907,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>357426</v>
+        <v>364892</v>
       </c>
       <c r="B4" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585914.2624319482</v>
+        <v>585941</v>
       </c>
       <c r="R4" t="n">
-        <v>7226140.63995935</v>
+        <v>7226152</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +945,9 @@
           <t>2011-07-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2011-07-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,7 +962,7 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1023,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1972001</v>
+        <v>357426</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585933.8427984505</v>
+        <v>585914</v>
       </c>
       <c r="R5" t="n">
-        <v>7226105.002790933</v>
+        <v>7226141</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,19 +1046,9 @@
           <t>2011-07-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2011-07-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,7 +1063,7 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1139,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>364892</v>
+        <v>877231</v>
       </c>
       <c r="B6" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585941.3311149593</v>
+        <v>586011</v>
       </c>
       <c r="R6" t="n">
-        <v>7226151.950587561</v>
+        <v>7225973</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,19 +1147,9 @@
           <t>2011-07-11</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2011-07-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,7 +1164,7 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -1255,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1972005</v>
+        <v>877232</v>
       </c>
       <c r="B7" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585945.379277747</v>
+        <v>585888</v>
       </c>
       <c r="R7" t="n">
-        <v>7226056.080602144</v>
+        <v>7226105</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,19 +1248,9 @@
           <t>2011-07-11</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2011-07-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,7 +1265,7 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -1371,15 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1971997</v>
+        <v>877233</v>
       </c>
       <c r="B8" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1411,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585934.4286240813</v>
+        <v>585868</v>
       </c>
       <c r="R8" t="n">
-        <v>7226113.860737666</v>
+        <v>7226125</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,19 +1349,9 @@
           <t>2011-07-11</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2011-07-11</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,7 +1366,7 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -1487,15 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1972000</v>
+        <v>7127715</v>
       </c>
       <c r="B9" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,37 +1393,41 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>SO Gaskeluokt, Ly lm</t>
+          <t>Långsjöby, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586022.805603078</v>
+        <v>586595</v>
       </c>
       <c r="R9" t="n">
-        <v>7226017.070974506</v>
+        <v>7225318</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1557,22 +1451,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2011-07-11</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-07-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2011-07-11</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-07-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Sveaskogs Naturvärdesinventering -Inventerare: Ebba Okfors  ID;29517</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,66 +1476,61 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Naturvärdesbedömning</t>
-        </is>
-      </c>
+          <t>Sveaskog genom Johan Ekenstedt</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1972002</v>
+        <v>7121714</v>
       </c>
       <c r="B10" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>SO Gaskeluokt, Ly lm</t>
+          <t>Långsjöby, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585858.3973765555</v>
+        <v>585765</v>
       </c>
       <c r="R10" t="n">
-        <v>7226133.967012323</v>
+        <v>7225654</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1673,22 +1557,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2011-07-11</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-07-12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2011-07-11</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-07-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Sveaskogs Naturvärdesinventering -Inventerare: Ebba Okfors  ID;29468</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,31 +1582,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Naturvärdesbedömning</t>
-        </is>
-      </c>
+          <t>Sveaskog genom Johan Ekenstedt</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1971998</v>
+        <v>1971996</v>
       </c>
       <c r="B11" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1759,10 +1629,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585918.0346907023</v>
+        <v>585887</v>
       </c>
       <c r="R11" t="n">
-        <v>7226097.807912569</v>
+        <v>7226108</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,19 +1662,9 @@
           <t>2011-07-11</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2011-07-11</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1819,7 +1679,7 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -1835,15 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>199922</v>
+        <v>1971997</v>
       </c>
       <c r="B12" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1851,21 +1706,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1875,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585944.1935782846</v>
+        <v>585934</v>
       </c>
       <c r="R12" t="n">
-        <v>7226154.980639124</v>
+        <v>7226114</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1908,19 +1763,9 @@
           <t>2011-07-11</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2011-07-11</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1935,7 +1780,7 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -1951,15 +1796,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>877231</v>
+        <v>1971998</v>
       </c>
       <c r="B13" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,21 +1807,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1991,10 +1831,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>586011.4421222114</v>
+        <v>585918</v>
       </c>
       <c r="R13" t="n">
-        <v>7225972.955298154</v>
+        <v>7226098</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2024,19 +1864,9 @@
           <t>2011-07-11</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2011-07-11</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2051,7 +1881,7 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
@@ -2067,15 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1971996</v>
+        <v>1972000</v>
       </c>
       <c r="B14" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585886.5404095224</v>
+        <v>586023</v>
       </c>
       <c r="R14" t="n">
-        <v>7226108.260824637</v>
+        <v>7226017</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2140,19 +1965,9 @@
           <t>2011-07-11</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2011-07-11</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2167,7 +1982,7 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -2183,15 +1998,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1972004</v>
+        <v>1972001</v>
       </c>
       <c r="B15" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2223,10 +2033,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585915.800667464</v>
+        <v>585934</v>
       </c>
       <c r="R15" t="n">
-        <v>7226116.687940931</v>
+        <v>7226105</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2256,19 +2066,9 @@
           <t>2011-07-11</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2011-07-11</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2283,7 +2083,7 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
@@ -2299,15 +2099,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>877232</v>
+        <v>1972002</v>
       </c>
       <c r="B16" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2315,21 +2110,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2339,10 +2134,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585887.9136923427</v>
+        <v>585858</v>
       </c>
       <c r="R16" t="n">
-        <v>7226104.511699351</v>
+        <v>7226134</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2372,19 +2167,9 @@
           <t>2011-07-11</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2011-07-11</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,7 +2184,7 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
@@ -2415,15 +2200,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>877233</v>
+        <v>1972003</v>
       </c>
       <c r="B17" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2431,21 +2211,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2455,10 +2235,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585868.3520574648</v>
+        <v>585996</v>
       </c>
       <c r="R17" t="n">
-        <v>7226124.993929903</v>
+        <v>7225980</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2488,19 +2268,9 @@
           <t>2011-07-11</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2011-07-11</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2515,7 +2285,7 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -2531,15 +2301,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>364888</v>
+        <v>1972004</v>
       </c>
       <c r="B18" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2547,21 +2312,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2571,10 +2336,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585942.5777843124</v>
+        <v>585916</v>
       </c>
       <c r="R18" t="n">
-        <v>7226050.947198521</v>
+        <v>7226117</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2604,19 +2369,9 @@
           <t>2011-07-11</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2011-07-11</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2631,7 +2386,7 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -2647,15 +2402,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>7121714</v>
+        <v>1972005</v>
       </c>
       <c r="B19" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2663,38 +2413,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Långsjöby, Ly lm</t>
+          <t>SO Gaskeluokt, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585764.8269726534</v>
+        <v>585945</v>
       </c>
       <c r="R19" t="n">
-        <v>7225653.810486494</v>
+        <v>7226056</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2721,27 +2467,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2011-07-12</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-07-11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2011-07-12</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Sveaskogs Naturvärdesinventering -Inventerare: Ebba Okfors  ID;29468</t>
+          <t>2011-07-11</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2756,27 +2487,26 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturvärdesbedömning</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>7127715</v>
+        <v>1972006</v>
       </c>
       <c r="B20" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2784,41 +2514,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Långsjöby, Ly lm</t>
+          <t>SO Gaskeluokt, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586595.0158938132</v>
+        <v>585854</v>
       </c>
       <c r="R20" t="n">
-        <v>7225317.946007272</v>
+        <v>7226134</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2842,27 +2568,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2011-07-12</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-07-11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2011-07-12</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Sveaskogs Naturvärdesinventering -Inventerare: Ebba Okfors  ID;29517</t>
+          <t>2011-07-11</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2877,27 +2588,26 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturvärdesbedömning</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>7126075</v>
       </c>
       <c r="B21" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2933,10 +2643,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585768.9103685061</v>
+        <v>585769</v>
       </c>
       <c r="R21" t="n">
-        <v>7225643.823327094</v>
+        <v>7225644</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2966,19 +2676,9 @@
           <t>2011-07-12</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2011-07-12</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
